--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-10 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.844</v>
+        <v>0.908</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>47.95</v>
+        <v>54.2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.732</v>
+        <v>0.725</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04547999858856201</v>
+        <v>0.04974999904632568</v>
       </c>
     </row>
     <row r="6">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>1.259</v>
+        <v>1.262</v>
       </c>
     </row>
     <row r="8">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>1071000000</v>
+        <v>1072000000</v>
       </c>
     </row>
     <row r="33">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>3672000000</v>
+        <v>3043000064</v>
       </c>
     </row>
     <row r="34">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669894.8070907</v>
+        <v>133741069.2250922</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>47.95</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6697171456</v>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>21.89</v>
-      </c>
+        <v>7248765952</v>
+      </c>
+      <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-12.43</v>
+        <v>-23.08</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1530,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>8950323200</v>
+        <v>8176083456</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.538602</v>
+        <v>22.369719</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.138999999999999</v>
+        <v>11.474</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.73</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="7">
@@ -1552,21 +1550,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TopBuild Corp.</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>11075025920</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>22.119448</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>14.041</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>2.548</v>
-      </c>
+          <t>BLD</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="33" t="n"/>
+      <c r="F7" s="33" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1580,16 +1570,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>35002597376</v>
+        <v>34434834432</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>26.37584</v>
+        <v>24.327204</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>19.66</v>
+        <v>17.111</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.05</v>
+        <v>1.831</v>
       </c>
     </row>
     <row r="9">
@@ -1620,16 +1610,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6020858368</v>
-      </c>
-      <c r="D10" s="33" t="n">
-        <v>37.50136</v>
-      </c>
+        <v>5283246080</v>
+      </c>
+      <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>15.679</v>
+        <v>12.261</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.538</v>
+        <v>1.196</v>
       </c>
     </row>
     <row r="11">
@@ -1644,16 +1632,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14753025024</v>
+        <v>16601927680</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>36.855457</v>
+        <v>47.126247</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>17.551</v>
+        <v>18.423</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.365</v>
+        <v>1.369</v>
       </c>
     </row>
     <row r="12">
@@ -1668,16 +1656,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>4380593152</v>
+        <v>4612818944</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.19174</v>
+        <v>11.021085</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>10.554</v>
+        <v>10.525</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.897</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="13">
@@ -1692,14 +1680,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>367709408</v>
+        <v>300177248</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-64.55200000000001</v>
+        <v>11.297</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.189</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="15">
@@ -1746,9 +1734,7 @@
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D17" s="35" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="D17" s="35" t="n"/>
       <c r="E17" s="35" t="n"/>
       <c r="F17" s="35" t="n">
         <v>0</v>
